--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -905,6 +905,324 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120245253</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79115</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svultentjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>423574</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6821788</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120245278</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92030</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svultentjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>423511</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6821719</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120245261</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91840</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svultentjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>423574</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6821788</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jakob Wallin, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245253</v>
+        <v>120245261</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
         <v>120245278</v>
       </c>
       <c r="B5" t="n">
-        <v>92030</v>
+        <v>92048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120245261</v>
+        <v>120245253</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>79131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245261</v>
+        <v>120245253</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120245253</v>
+        <v>120245261</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245253</v>
+        <v>120245261</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245278</v>
+        <v>120245253</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>79131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423511</v>
+        <v>423574</v>
       </c>
       <c r="R5" t="n">
-        <v>6821719</v>
+        <v>6821788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120245261</v>
+        <v>120245278</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>92048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423574</v>
+        <v>423511</v>
       </c>
       <c r="R6" t="n">
-        <v>6821788</v>
+        <v>6821719</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245261</v>
+        <v>120245253</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1006,17 +1006,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Carl Jansson</t>
+          <t>Carl Jansson, Jakob Wallin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245253</v>
+        <v>120245278</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423574</v>
+        <v>423511</v>
       </c>
       <c r="R5" t="n">
-        <v>6821788</v>
+        <v>6821719</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,17 +1112,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Carl Jansson</t>
+          <t>Carl Jansson, Jakob Wallin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120245278</v>
+        <v>120245261</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>423511</v>
+        <v>423574</v>
       </c>
       <c r="R6" t="n">
-        <v>6821719</v>
+        <v>6821788</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jakob Wallin, Carl Jansson</t>
+          <t>Carl Jansson, Jakob Wallin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Jakob Wallin</t>
+          <t>Jakob Wallin, Carl Jansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Jakob Wallin</t>
+          <t>Jakob Wallin, Carl Jansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Jakob Wallin</t>
+          <t>Jakob Wallin, Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 9786-2024 artfynd.xlsx
+++ b/artfynd/A 9786-2024 artfynd.xlsx
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120245253</v>
+        <v>120245278</v>
       </c>
       <c r="B4" t="n">
-        <v>79131</v>
+        <v>92048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>423574</v>
+        <v>423511</v>
       </c>
       <c r="R4" t="n">
-        <v>6821788</v>
+        <v>6821719</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120245278</v>
+        <v>120245253</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>79131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,21 +1029,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2079</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>423511</v>
+        <v>423574</v>
       </c>
       <c r="R5" t="n">
-        <v>6821719</v>
+        <v>6821788</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
